--- a/icb_urls.xlsx
+++ b/icb_urls.xlsx
@@ -756,7 +756,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>KEEP this URL - it holds no PDFs itself but it is the only page carrying BOTH the forward meeting schedule AND a link to the current/next meeting's own page where the pack lands, so it works as a one-hop hub. Repointing to /previous-board-meetings/ would blind a crawler to upcoming packs. Strategy: fetch the landing, follow any href matching board-meeting-held-in-public-* for the current pack, and separately follow /previous-board-meetings/ (24 dated links, July 2022 to March 2026) for backfill. Each per-meeting page carries 23-46 SEPARATE /media/{8-char-hash}/item-NN-*.pdf files - there is NO consolidated board pack, so a pack analyser must pull them all. Slugs are unguessable: the weekday is embedded inconsistently (...on-wednesday-29-july-2026, ...on-tuesday-31-march-2026, ...tuesday-25-march-2025 with no 'on', ...28-november-2023 with no weekday) - always scrape hrefs, never construct them. Filter on the board-meeting-held-in-public- prefix to isolate the ICB Board: the ICP lives under /previous-integrated-care-partnership-icp-meetings/ and AGMs under /annual-general-meetings/, and the 29 July 2026 AGM ran immediately before the Board on the same day. Beware: extraordinary board meetings (16 June 2026, 12 February 2026) are never archived - they surface only as draft-minutes items inside the next ordinary pack. Umbraco CMS, plain server-rendered HTML, no JS and no anti-bot; sitemap.xml 404s.</t>
+          <t>KEEP this URL - it holds no PDFs itself but it is the only page carrying BOTH the forward meeting schedule AND a link to the current/next meeting's own page where the pack lands, so it works as a one-hop hub. Repointing to /previous-board-meetings/ would blind a crawler to upcoming packs. Strategy: fetch the landing, follow any href matching board-meeting-held-in-public-* for the current pack, and separately follow /previous-board-meetings/ (24 dated links, July 2022 to March 2026) for backfill. Each per-meeting page carries 23-46 SEPARATE /media/{8-char-hash}/item-NN-*.pdf files - there is NO consolidated board pack, so a pack analyser must pull them all. Slugs are unguessable: the weekday is embedded inconsistently (...on-wednesday-29-july-2026, ...on-tuesday-31-march-2026, ...tuesday-25-march-2025 with no 'on', ...28-november-2023 with no weekday) - always scrape hrefs, never construct them. Filter on the board-meeting-held-in-public- prefix to isolate the ICB Board: the ICP lives under /previous-integrated-care-partnership-icp-meetings/ and AGMs under /annual-general-meetings/, and the 29 July 2026 AGM ran immediately before the Board on the same day. Beware: extraordinary board meetings (16 June 2026, 12 February 2026) are never archived - they surface only as draft-minutes items inside the next ordinary pack. Umbraco CMS, plain server-rendered HTML, no JS and no anti-bot; sitemap.xml 404s. Re-verified 2026-09-12 by browser-UA curl (200, 35KB): landing intact, newest held meeting 29 July 2026 and dates scheduled to 31 March 2027; papers remain one hop deeper on the per-meeting sub-pages, which is the standing reason for the partial score.</t>
         </is>
       </c>
       <c r="N5" t="b">
@@ -774,7 +774,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-09-05: WebFetch reached the page; landing links the 29 July 2026 meeting sub-page plus a 'Previous Board meetings' archive - papers sit one hop deeper, which is why the validator scores it partial.</t>
+          <t>2026-09-12: browser-UA curl returned HTTP 200 (35KB); the landing links the 29 July 2026 meeting plus the previous-meetings archive, with 30 September 2026, 25 November 2026, 27 January 2027 and 31 March 2027 scheduled.</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>The ICB site is a static server-rendered front-end; WebFetch works, no Playwright. /meetings/board-papers holds the NEXT meeting's pack; /meetings/past-board-papers is the dated archive (back to 2022, each date a heading with its PDF list). Board meets bi-monthly (odd months). All PDF hrefs point at the sister domain www.hwics.org.uk via /download_file/&lt;id&gt;/&lt;collection&gt; -- collection 414 = current pack, 463 = past-papers archive (numeric endpoints, not .pdf-suffixed). Single-ICB board, no ICP/Joint pages intermixed on these two pages; AGM material is bundled into the July board pack -- treat as ICB Board. Prefer /meetings/board-papers for the imminent pack and /meetings/past-board-papers to backfill.</t>
+          <t>The ICB site is a static server-rendered front-end; WebFetch works, no Playwright. /meetings/board-papers holds the NEXT meeting's pack; /meetings/past-board-papers is the dated archive (back to 2022, each date a heading with its PDF list). Board meets bi-monthly (odd months). All PDF hrefs point at the sister domain www.hwics.org.uk via /download_file/&lt;id&gt;/&lt;collection&gt; -- collection 414 = current pack, 463 = past-papers archive (numeric endpoints, not .pdf-suffixed). Single-ICB board, no ICP/Joint pages intermixed on these two pages; AGM material is bundled into the July board pack -- treat as ICB Board. Prefer /meetings/board-papers for the imminent pack and /meetings/past-board-papers to backfill. Re-verified 2026-09-12 by browser-UA curl (200, 53KB): the landing now holds the forthcoming 16 September 2026 pack as 10 /download_file/&lt;id&gt;/414 links on the hwics.org.uk sister domain, confirming the current-pack/archive split still holds.</t>
         </is>
       </c>
       <c r="N12" t="b">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-09-05: WebFetch reached the page; 15 documents for the 15 July 2026 public board, served as https://www.hwics.org.uk/download_file/{id}/414 links.</t>
+          <t>2026-09-12: browser-UA curl returned HTTP 200 (53KB) with 10 www.hwics.org.uk/download_file/ links for the 16 September 2026 public board.</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Static HTML landing renders fine via WebFetch (no Playwright). Lists ICB Board meeting dates every two months; each date links to a per-meeting event page at /board-meetings/north-east-london-icb-board-meeting-NN/ holding papers as /download-attachment/NNNNN links (the main board pack plus separate minutes/questions-log); underlying files live at /wp-content/uploads/YYYY/MM/. Papers publish at least 5 working days before each meeting, so the newest future date shows no PDFs until then. Filter to the NHS North East London ICB Board -- skip the ICP packs, borough Partnership Boards, Health &amp; Wellbeing boards, and named sub-committees. Flag 2026-08-01: the landing's meeting list showed nothing later than 31 March 2026 on this run -- if a crawler finds no current pack here, check the /events/ pages directly before assuming a fetch failure. Update 2026-08-15: the landing's own upcoming-meetings list is stale (newest entry 31 Mar 2026). The live index is /board-meetings/, which carries meeting 22 (14 May 2026) and meeting 23 (23 July 2026). Crawl /board-meetings/ for current packs and treat the landing as background only.</t>
+          <t>Static HTML landing renders fine via WebFetch (no Playwright). Lists ICB Board meeting dates every two months; each date links to a per-meeting event page at /board-meetings/north-east-london-icb-board-meeting-NN/ holding papers as /download-attachment/NNNNN links (the main board pack plus separate minutes/questions-log); underlying files live at /wp-content/uploads/YYYY/MM/. Papers publish at least 5 working days before each meeting, so the newest future date shows no PDFs until then. Filter to the NHS North East London ICB Board -- skip the ICP packs, borough Partnership Boards, Health &amp; Wellbeing boards, and named sub-committees. Flag 2026-08-01: the landing's meeting list showed nothing later than 31 March 2026 on this run -- if a crawler finds no current pack here, check the /events/ pages directly before assuming a fetch failure. Update 2026-08-15: the landing's own upcoming-meetings list is stale (newest entry 31 Mar 2026). The live index is /board-meetings/, which carries meeting 22 (14 May 2026) and meeting 23 (23 July 2026). Crawl /board-meetings/ for current packs and treat the landing as background only. Re-verified 2026-09-12: /board-meetings/ is still the live index (200, dates through 9 September 2026, paginating at /category/board-meetings/page/2/) while the landing at the DB URL yielded no meeting dates whatsoever this run. Keep crawling /board-meetings/ and filter out the primary-care-contracts and other sub-committee entries that share that path.</t>
         </is>
       </c>
       <c r="N23" t="b">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-22: the 29 July 2026 event page (/board-meetings/north-east-london-icb-board-meeting-23/) carries the 6MB 'NHS North East London ICB Board - 29 July 2026' pack plus an item-8.1 governance appendices pack. Note the landing renders meeting dates without years, which is why page summarisers misread the list as 2024.</t>
+          <t>2026-09-12: the /board-meetings/ index returned HTTP 200 with meeting dates through 9 September 2026, while the DB landing page again returned no meeting dates at all - the landing remains background only.</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Newly merged ICB (April 2026, ex-North West London / Z9B2Z). The board-meetings landing (/how-we-are-run/meetings/w-plus-nl-board-meetings) is static HTML and lists upcoming ICB Board-of-Members dates plus a section linking into the document library at /how-we-are-run/policies-and-publications/navigate/{id}/2410. That library groups papers into per-meeting folders (1 Apr 2026, 17 Jun 2026, 22 Jul 2026, ...); each folder lists individual /download_file/{uuid}/{n} PDFs. Filter to the ICB Board of Members -- SKIP the PCCG folder, the ICP pages, and the Primary Care Commissioning Committee. First packs already fully populated (22 Jul 2026 pack has 13 papers). Static WebFetch is sufficient.</t>
+          <t>Newly merged ICB (April 2026, ex-North West London / Z9B2Z). The board-meetings landing (/how-we-are-run/meetings/w-plus-nl-board-meetings) is static HTML and lists upcoming ICB Board-of-Members dates plus a section linking into the document library at /how-we-are-run/policies-and-publications/navigate/{id}/2410. That library groups papers into per-meeting folders (1 Apr 2026, 17 Jun 2026, 22 Jul 2026, ...); each folder lists individual /download_file/{uuid}/{n} PDFs. Filter to the ICB Board of Members -- SKIP the PCCG folder, the ICP pages, and the Primary Care Commissioning Committee. First packs already fully populated (22 Jul 2026 pack has 13 papers). Static WebFetch is sufficient. Re-verified 2026-09-12 by browser-UA curl (200, 76KB): landing intact with the 22 July 2026 pack linked and dates scheduled to 24 March 2027; the papers themselves stay in the /navigate/{id}/2410 library one hop deeper, which is why the landing scores thin.</t>
         </is>
       </c>
       <c r="N26" t="b">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>2026-09-05: WebFetch reached the page; newest entry 'Board meeting - 22 July 2026 - agenda papers' linking into the /navigate/486/2410 document library.</t>
+          <t>2026-09-12: browser-UA curl returned HTTP 200 (76KB); the landing lists the 22 July 2026 papers plus 23 September 2026, 21 October 2026, 27 January 2027 and 24 March 2027 scheduled, with the document library one hop deeper.</t>
         </is>
       </c>
     </row>

--- a/icb_urls.xlsx
+++ b/icb_urls.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-09-12: browser-UA curl returned HTTP 200 (35KB); the landing links the 29 July 2026 meeting plus the previous-meetings archive, with 30 September 2026, 25 November 2026, 27 January 2027 and 31 March 2027 scheduled.</t>
+          <t>Re-confirmed 2026-09-19 via WebFetch: hub works as documented - links the current meeting page (board-meeting-held-in-public-on-wednesday-29-july-2026) and the Previous Board meetings archive. papers_partial reflects that the hub holds no PDFs itself.</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-09-12: browser-UA curl returned HTTP 200 (53KB) with 10 www.hwics.org.uk/download_file/ links for the 16 September 2026 public board.</t>
+          <t>Re-confirmed 2026-09-19 via WebFetch: /meetings/board-papers currently carries the 16 September 2026 public board pack as 10 separate PDFs, with the dated archive at /meetings/past-board-papers.</t>
         </is>
       </c>
     </row>
@@ -2128,17 +2128,17 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>papers_partial</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2026-09-12: the /board-meetings/ index returned HTTP 200 with meeting dates through 9 September 2026, while the DB landing page again returned no meeting dates at all - the landing remains background only.</t>
+          <t>Re-confirmed 2026-09-19 via WebFetch: landing renders and links per-meeting event pages under /board-meetings/, though the statically-rendered listing surfaces older meetings first - crawlers should page through rather than trust the first entries.</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>2026-09-12: browser-UA curl returned HTTP 200 (76KB); the landing lists the 22 July 2026 papers plus 23 September 2026, 21 October 2026, 27 January 2027 and 24 March 2027 scheduled, with the document library one hop deeper.</t>
+          <t>Re-confirmed 2026-09-19 via WebFetch: landing lists the 22 July 2026 board meeting with agenda papers in the /navigate/486/2410 document library plus a recording. The no_papers_visible flag was a local-fetch false negative.</t>
         </is>
       </c>
     </row>

--- a/icb_urls.xlsx
+++ b/icb_urls.xlsx
@@ -1176,25 +1176,25 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Current URL is correct and live; the reported failure is a WAF/bot 403 that only blocks WebFetch — load it in Playwright (page title 'ICB Board Meetings - Happy Healthy Lives' confirms). The org now runs as the CWHW cluster (Coventry &amp; Warwickshire + Herefordshire &amp; Worcestershire), so packs are labelled 'CWHW ICB Board' or 'CWICB Board'. Meeting papers sit inside JavaScript accordions per meeting date whose individual PDF links load dynamically on expand; the real files live at /download/clientfiles/files/. Google site:happyhealthylives.uk with the file path is the fastest way to surface a specific pack URL.</t>
+          <t>The URL is correct and live. Route picture as of 2026-09-26: local browser-UA curl reaches it cleanly (HTTP 200, 56KB) and - importantly - the raw HTML already contains every paper href, so the local static path is sufficient and Playwright is NOT required (needs_playwright dropped to false this run). Server-side WebFetch is the route that is blocked here (ECONNRESET / 403); Playwright also works if you need it, so never read a block on one route as proof the page is unreachable. The org runs as the CWHW cluster (Coventry &amp; Warwickshire + Herefordshire &amp; Worcestershire), so packs are labelled 'CWHW ICB Board', 'Public Board', or the legacy 'CWICB Board'. Papers are NOT a single combined pack: each agenda item is its own file under /download/clientfiles/files/ named 'Agenda {NN}[{i}] {Title} {D Mon YY}.pdf', with 'Agenda 00 ... Agenda' the agenda itself, and a few items (the board governance log) are .xlsx rather than PDF. The page renders as per-meeting accordions but the hrefs sit in the static HTML, so harvest all /download/clientfiles/files/ links and group them by the meeting date carried in the filename. Forward schedule currently 16 September 2026, 18 November 2026, 20 January 2027, 17 March 2027; the July meeting doubles as the AGM ('AGM &amp; Public Board 15 July 26'). Google site:happyhealthylives.uk plus the file path remains the fastest way to surface one specific pack.</t>
         </is>
       </c>
       <c r="N11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>/download/clientfiles/files/ host path for all packs;Filenames like 'Papers for the {DD} {Mon} {YYYY} CWICB Board meeting';'CWHW ICB Board' prefix on cluster governance docs;Often split into PACK 1 / PACK 2 / PACK 3;Accordion grouped by meeting date on the landing page</t>
+          <t>/download/clientfiles/files/Agenda%20{NN}%20{Title}%20{D}%20{Mon}%20{YY}.pdf;'Agenda 00 ... Agenda' = the agenda itself;'Public Board';'CWHW ICB Board';legacy 'CWICB Board'</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>ICP Board;Integrated Care Partnership;Joint Committee;Committee Escalation;Herefordshire &amp; Worcestershire-only board</t>
+          <t>Governance Log (.xlsx);'Board Notes';draft minutes;Annual Report;ICP / Integrated Care Partnership;(1) duplicate-suffixed files</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Live landing page confirmed via Playwright with dated 2026 board entries and a recent example pack (19 Nov 2025 CWICB Board meeting papers) on-domain.</t>
+          <t>Re-confirmed 2026-09-26 via local browser-UA curl (HTTP 200, 56KB, title 'ICB Board Meetings - Happy Healthy Lives'): per-agenda-item PDFs current to the 16 September 2026 public board, forward dates listed to 17 March 2027. needs_playwright dropped to false because the raw HTML already carries every paper href. Server-side WebFetch was ECONNRESET this run.</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2383,7 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.hantsiow.icb.nhs.uk/icb/integrated-care-board-meetings/</t>
+          <t>https://www.hantsiow.icb.nhs.uk/icb/integrated-care-board-meetings</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Pattern C: the integrated-care-board-meetings landing is static HTML listing dated ICB Board meetings, each linking to a per-meeting sub-page of the form /icb/integrated-care-board-meetings/navigate/23515/&lt;id&gt;. Each per-meeting page does NOT offer a single combined pack; instead it lists numbered individual paper PDFs (Paper 0 Agenda, Paper 2a Minutes, Paper 4 Chair report, Paper 5 CEO report, Paper 6 BAF, etc.), each downloaded via /download_file/&lt;file-id&gt;/452. To assemble a full pack a crawler must follow each meeting page and fetch all Paper N download_file links (the agenda is 'Paper 0 - Public Agenda'). The /navigate/23515/ branch is the ICB Board; skip other committee/ICP listings.</t>
+          <t>Pattern C, refreshed 2026-09-26. NOTE the canonical URL has NO trailing slash - the trailing-slash form 301-redirects here, and the DB now stores the redirect target, so a crawler saves a hop. The integrated-care-board-meetings landing is static HTML (local browser-UA curl: HTTP 200, 82KB) listing dated ICB Board meetings, each linking to a per-meeting sub-page of the form /icb/integrated-care-board-meetings/navigate/23515/&lt;id&gt;. Each per-meeting page does NOT offer a single combined pack; instead it lists numbered individual paper PDFs (Paper 0 Agenda, Paper 2a Minutes, Paper 4 Chair report, Paper 5 CEO report, Paper 6 BAF, etc.), each downloaded via /download_file/&lt;file-id&gt;/452. To assemble a full pack a crawler must follow each meeting page and fetch all Paper N download_file links (the agenda is 'Paper 0'). The board meets roughly bi-monthly; the listing currently spans 5 February 2025 through 4 November 2026. Server-side WebFetch socket-hangs on this host, so prefer the local static path here - the reverse of most orgs in this DB.</t>
         </is>
       </c>
       <c r="N27" t="b">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Per-meeting page for 5 November 2025 confirmed listing ~19 individual numbered paper PDFs via /download_file/ links; no single combined pack is published.</t>
+          <t>Re-confirmed 2026-09-26 via local browser-UA curl following the site's own 301 to the no-trailing-slash canonical (HTTP 200, 82KB, title 'Integrated Care Board meetings :: NHS Hampshire and Isle of Wight'): 15+ /navigate/23515/&lt;id&gt; per-meeting pages spanning 5 February 2025 to 4 November 2026, most recent held meeting 2 September 2026. DB url updated to the redirect target. Server-side WebFetch socket-hangs on this host.</t>
         </is>
       </c>
     </row>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>2026-09-05: WebFetch reached the page; packs hosted on docs.cios.icb.nhs.uk with per-year archive sections, newest the 28 May 2026 extraordinary meeting.</t>
+          <t>Re-confirmed 2026-09-26 via server-side WebFetch (HTTP 200, title 'Meetings in public - NHS Cornwall and Isles of Scilly'): docs.cios.icb.nhs.uk pack links intact. PUBLICATION GAP - the newest entry is still the 28 May 2026 extraordinary meeting, the page is 'last reviewed 27 May 2026' and says the next board date 'will be published in due course'. Watch for papers migrating to the SW-PEN cluster board at swpboard.nhs.uk.</t>
         </is>
       </c>
     </row>

--- a/icb_urls.xlsx
+++ b/icb_urls.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Re-confirmed 2026-09-19 via WebFetch: hub works as documented - links the current meeting page (board-meeting-held-in-public-on-wednesday-29-july-2026) and the Previous Board meetings archive. papers_partial reflects that the hub holds no PDFs itself.</t>
+          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 36KB): hub links the 30 September 2026 board-in-public page (41 /media/{hash}/*.pdf items); next date 25 Nov 2026.</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Re-confirmed 2026-09-26 via local browser-UA curl (HTTP 200, 56KB, title 'ICB Board Meetings - Happy Healthy Lives'): per-agenda-item PDFs current to the 16 September 2026 public board, forward dates listed to 17 March 2027. needs_playwright dropped to false because the raw HTML already carries every paper href. Server-side WebFetch was ECONNRESET this run.</t>
+          <t>Re-verified 2026-10-03 by local browser-UA curl with --retry (200, 56KB; WebFetch got ECONNRESET): static HTML holds /download/clientfiles/files/ links for the 16 Sep 2026 Public Board; next meeting 18 Nov 2026.</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Re-confirmed 2026-09-19 via WebFetch: /meetings/board-papers currently carries the 16 September 2026 public board pack as 10 separate PDFs, with the dated archive at /meetings/past-board-papers.</t>
+          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 53KB): /meetings/board-papers holds the 16 September 2026 pack as 10 hwics.org.uk/download_file/&lt;id&gt;/414 links; past-board-papers lists 2026 meetings to 15 July.</t>
         </is>
       </c>
     </row>
@@ -2128,17 +2128,17 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>papers_partial</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Re-confirmed 2026-09-19 via WebFetch: landing renders and links per-meeting event pages under /board-meetings/, though the statically-rendered listing surfaces older meetings first - crawlers should page through rather than trust the first entries.</t>
+          <t>Re-verified 2026-10-03 by local browser-UA curl: the stored landing links per-meeting pages through ICB Board meeting 23, whose page holds the 'NHS North East London ICB Board - 29 July 2026' pack (/download-attachment/55670); meeting 24 not yet posted.</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Re-confirmed 2026-09-19 via WebFetch: landing lists the 22 July 2026 board meeting with agenda papers in the /navigate/486/2410 document library plus a recording. The no_papers_visible flag was a local-fetch false negative.</t>
+          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 76KB): landing links the 22 July 2026 Board papers folder (navigate/486/2410) and the 23 Sep 2026 AGM folder (navigate/1617/2410).</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://cios.icb.nhs.uk/about/meetings/</t>
+          <t>https://swpboard.nhs.uk/board-meetings/board-meeting-papers-and-minutes/</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>The current URL is in fact live and correct (last reviewed 27 May 2026) — the reported breakage did not reproduce; WebFetch returns it cleanly. Reach it via About Us &gt; Meetings. Packs are grouped by financial year (2025-26, 2024-25, etc.) with direct PDFs hosted on a separate docs subdomain at docs.cios.icb.nhs.uk/DocumentsLibrary/NHSCornwallAndIslesOfScilly/Organisation/PublicMeetings/BoardMeetings/{YYYY}/{YYYYMM}/. The ICB now operates in a cluster with NHS Devon, and recent sessions are 'Extraordinary' or AGM, but the board pack is published on its own cios.icb.nhs.uk domain.</t>
+          <t>URL PATCHED 2026-10-03 (Pattern F + cluster board): NHS Cornwall and Isles of Scilly ICB now holds its ordinary board meetings jointly with NHS Devon ICB (QJK) as the 'South West Peninsula Board' (SW-PEN cluster), and the packs are published on the dedicated joint site swpboard.nhs.uk (site title 'NHS CIOS and Devon ICB'). The old own-domain page cios.icb.nhs.uk/about/meetings/ is still live but stops at the 28 May 2026 extraordinary meeting and says future dates are TBC; use it only for the pre-cluster archive (direct PDFs on docs.cios.icb.nhs.uk/DocumentsLibrary/NHSCornwallAndIslesOfScilly/Organisation/PublicMeetings/BoardMeetings/{YYYY}/{YYYYMM}/, grouped by financial year). Strategy on the new landing: static WordPress page (plain browser-UA curl works, no Playwright) listing each joint meeting with direct PDFs under /wp-content/uploads/YYYY/MM/. Naming varies by meeting: 'SWPB-Public-29.01.2026-Meeting-Papers-1.pdf', 'SWPB-Meeting-30-July-2026-Agenda-and-Papers-v4.pdf', 'SWP-Board-24.09.2026-Agenda-and-Reports.pdf'. Take the 'Meeting Papers' / 'Agenda and Papers' / 'Agenda and Reports' file as the main pack; separate 'Appendices' PDFs and individual SWPB26-NNN item PDFs accompany it, and minutes are uploaded months later. Bi-monthly cadence (Jan, Mar, May, Jul, Sep, Nov); next 26 Nov 2026. The joint AGM pack (NHS-CIOS-and-NHSD-AGM-*) is also listed. Note the swpboard.nhs.uk/meetings/ path recorded as cluster_meeting_url now 404s - this page is the live joint archive.</t>
         </is>
       </c>
       <c r="N36" t="b">
@@ -3037,17 +3037,17 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>docs.cios.icb.nhs.uk/DocumentsLibrary/.../BoardMeetings/{fy e.g. 2526}/{yyyymm}/ path;Separate PDFs per item: Agenda, DOI Register, Minutes, individual reports;Filenames like Agenda...{Month}{Year}.pdf;Grouped by financial year on the landing page</t>
+          <t>swpboard.nhs.uk/wp-content/uploads/YYYY/MM/SWP*-*.pdf;Agenda-and-Papers / Agenda-and-Reports / Meeting-Papers = main pack;South West Peninsula Board;pre-cluster archive: docs.cios.icb.nhs.uk/DocumentsLibrary/.../BoardMeetings/{fy}/{yyyymm}/</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Integrated Care Partnership;ICP;Joint Committee;Cluster governance committee</t>
+          <t>Integrated Care Partnership;ICP;Joint Committee;Cluster governance committee;Minutes</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Re-confirmed 2026-09-26 via server-side WebFetch (HTTP 200, title 'Meetings in public - NHS Cornwall and Isles of Scilly'): docs.cios.icb.nhs.uk pack links intact. PUBLICATION GAP - the newest entry is still the 28 May 2026 extraordinary meeting, the page is 'last reviewed 27 May 2026' and says the next board date 'will be published in due course'. Watch for papers migrating to the SW-PEN cluster board at swpboard.nhs.uk.</t>
+          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 125KB): swpboard.nhs.uk lists the joint board's 2026 packs (29 Jan, 26 Mar, 28 May, 30 Jul, 24 Sep 2026 - SWP-Board-24.09.2026-Agenda-and-Reports.pdf); the old cios.icb.nhs.uk page stops at the 28 May 2026 extraordinary meeting.</t>
         </is>
       </c>
     </row>

--- a/icb_urls.xlsx
+++ b/icb_urls.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 36KB): hub links the 30 September 2026 board-in-public page (41 /media/{hash}/*.pdf items); next date 25 Nov 2026.</t>
+          <t>Re-verified 2026-10-10 by local browser-UA curl (200, 36KB): hub links the 'Board meeting held in public on Wednesday 30 September 2026' page.</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Strategy: landing lists per-meeting entries (27 dated meeting links this run); each links to its own sub-page of PDFs (agenda, papers, finance). Filter to the main Board (skip ICP/committee/joint). Prefer the largest 'Agenda and Papers' combined PDF. Static fetch works. Pattern C.</t>
+          <t>Strategy: the landing lists each 'NHS West Yorkshire ICB Board Meeting - &lt;d Month yyyy&gt;' as a sub-page at /meetings/integrated-care-board/nhs-west-yorkshire-icb-&lt;d-month-yyyy&gt;; each sub-page carries the agenda, the combined papers PDF and any supplementary items. Extraordinary meetings are listed with that prefix. Static fetch works (plain curl 200, no WAF). Follow each meeting link and prefer the combined board papers PDF; skip the annual report and accounts entries that share the landing. Pattern C. Refreshed 2026-10-10: newest meeting 22 September 2026.</t>
         </is>
       </c>
       <c r="N8" t="b">
@@ -947,17 +947,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Agenda and Papers;Combined Pack;Public Board Pack</t>
+          <t>nhs-west-yorkshire-icb-&lt;d-month-yyyy&gt;;Board papers;Agenda and papers</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>Annual Report and Accounts;Minutes only;Q&amp;A</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=0, year_archives=2, meeting_subpages=27.</t>
+          <t>Refreshed 2026-10-10 by local browser-UA curl (200, 83KB): per-meeting pages for 10 Feb (extraordinary), 24 Mar, 15 Jun, 23 Jun and 22 September 2026 (/meetings/integrated-care-board/nhs-west-yorkshire-icb-22-september-2026).</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 by local browser-UA curl with --retry (200, 56KB; WebFetch got ECONNRESET): static HTML holds /download/clientfiles/files/ links for the 16 Sep 2026 Public Board; next meeting 18 Nov 2026.</t>
+          <t>Re-verified 2026-10-10 by local browser-UA curl with --retry (200, 56KB; validator saw a connection reset): static HTML holds 'Agenda 00 Public Board 16 September 26' and the other 16 Sep 2026 items under /download/clientfiles/files/.</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 53KB): /meetings/board-papers holds the 16 September 2026 pack as 10 hwics.org.uk/download_file/&lt;id&gt;/414 links; past-board-papers lists 2026 meetings to 15 July.</t>
+          <t>Re-verified 2026-10-10 by local browser-UA curl (200, 53KB): /meetings/board-papers holds the 16 September 2026 pack (Agenda 00 Public Board 16 September 26, BAF, governance log) as hwics.org.uk/download_file/&lt;id&gt;/414 links.</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Strategy: landing surfaces board papers directly (mix of dated PDFs and/or year links). Static fetch works. Prefer the main combined board pack; filter observer notes and Q&amp;A. Pattern A/B.</t>
+          <t>Strategy: the landing lists each board meeting as an event page (/events/icb-board-meeting-&lt;date&gt;/) and a document page (/documents/board-meeting-agenda-and-reports-&lt;d-month-yyyy&gt;/ - the newest uses the shorter /documents/board-meeting-&lt;d-month-yyyy&gt;/ slug, so scrape hrefs rather than building them); the document page holds the combined agenda-and-reports PDF. Separate 'Board questions and responses' documents accompany each meeting. Bi-monthly cadence (Apr, May, Jul, Sep 2026 so far). Static fetch works (plain curl 200, no WAF; contact pages use Cloudflare email obfuscation but the board pages do not). Prefer the agenda-and-reports document; skip questions-and-responses and minutes-only files. Pattern C. Refreshed 2026-10-10: newest meeting 23 September 2026.</t>
         </is>
       </c>
       <c r="N22" t="b">
@@ -2043,17 +2043,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+          <t>Board meeting agenda and reports;/documents/board-meeting-agenda-and-reports-&lt;date&gt;/;/documents/board-meeting-&lt;date&gt;/</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>questions and responses;Minutes only</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=0, year_archives=0, meeting_subpages=8.</t>
+          <t>Refreshed 2026-10-10 by local browser-UA curl (200, 58KB): 'Board meeting agenda and reports' document pages for 1 Apr, 20 May, 15 Jul and 23 September 2026 (/documents/board-meeting-23-september-2026/) plus matching event pages.</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 by local browser-UA curl: the stored landing links per-meeting pages through ICB Board meeting 23, whose page holds the 'NHS North East London ICB Board - 29 July 2026' pack (/download-attachment/55670); meeting 24 not yet posted.</t>
+          <t>Re-verified 2026-10-10 by local browser-UA curl (200, 218KB): the stored landing links per-meeting pages through ICB Board meeting 23 (29 Jul 2026), and the live /board-meetings/ index likewise stops at meeting 23; meeting-24 is still 404, so no board pack has appeared since July.</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Strategy: landing lists year archives (3 year links this run, e.g. 'Board papers 2025'). Follow each year link to dated PDF listings; main packs typically 5-30MB. Static fetch works. Pattern B.</t>
+          <t>Strategy: /publications/ is a mixed publications index (annual reports, plans, engagement reports) in which board packs appear as entries titled 'Board papers - &lt;Month Year&gt;' linking to a sub-page (/publications/board-papers-&lt;month&gt;-&lt;year&gt;/) that holds the PDF(s) for that meeting; older years sit behind year links. Static fetch works (plain curl 200, no WAF; the contact pages use Cloudflare email obfuscation but the publications pages do not). Filter entries to those starting 'Board papers' and follow each to its PDF; ignore the other publication types. Pattern B/C. Refreshed 2026-10-10: newest entry Board papers - July 2026.</t>
         </is>
       </c>
       <c r="N25" t="b">
@@ -2250,17 +2250,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Board Papers;Public Board Pack</t>
+          <t>Board papers - &lt;Month Year&gt;;/publications/board-papers-&lt;month&gt;-&lt;year&gt;/</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>Annual report;engagement report;Capital resource use plan;Minutes only</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=0, year_archives=3, meeting_subpages=3.</t>
+          <t>Refreshed 2026-10-10 by local browser-UA curl (200, 78KB): /publications/ lists dated publication entries; the newest board entry is 'Board papers - July 2026' (/publications/board-papers-july-2026/); no September or October 2026 entry yet (both slugs 404).</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 76KB): landing links the 22 July 2026 Board papers folder (navigate/486/2410) and the 23 Sep 2026 AGM folder (navigate/1617/2410).</t>
+          <t>Re-verified 2026-10-10 by local browser-UA curl (200, 76KB): landing links the 22 July 2026 Board papers folder (navigate/486/2410) and the 23 Sep 2026 AGM folder (navigate/1617/2410); next board meeting 21 Oct 2026, papers to follow.</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Strategy: landing lists per-meeting entries (18 dated meeting links this run); each links to its own sub-page of PDFs (agenda, papers, finance). Filter to the main Board (skip ICP/committee/joint). Prefer the largest 'Agenda and Papers' combined PDF. Static fetch works. Pattern C.</t>
+          <t>Strategy: the /events-calender landing lists upcoming board meetings as event sub-pages (/events-calender/event/board-meeting-&lt;month&gt;-&lt;year&gt;-&lt;n&gt;/) and, lower down, past meetings with their packs linked directly as /download/icb-board-meeting-pack-&lt;month&gt;-&lt;year&gt;.pdf?ver=&lt;n&gt;&amp;doc=&lt;id&gt;.pdf (Part 1 = public). Static fetch works (plain curl 200, no WAF). Harvest the 'ICB Board meeting pack' links from the landing; skip minutes-only files and non-board events. Pattern A with event sub-pages. Refreshed 2026-10-10: newest pack July 2026, next meeting November 2026.</t>
         </is>
       </c>
       <c r="N28" t="b">
@@ -2479,17 +2479,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Agenda and Papers;Combined Pack;Public Board Pack</t>
+          <t>icb-board-meeting-pack-&lt;month&gt;-&lt;year&gt;.pdf;ICB Board (Part 1) meeting pack;/download/</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>minutes;Part 2;Minutes only</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=0, year_archives=0, meeting_subpages=18.</t>
+          <t>Refreshed 2026-10-10 by local browser-UA curl (200, 33KB): events calendar carries inline /download/icb-board-meeting-pack-&lt;month&gt;-&lt;year&gt;.pdf links, newest July 2026 (plus July 2026 minutes); upcoming board events Nov 2026, Feb and Mar 2027.</t>
         </is>
       </c>
     </row>
@@ -2769,7 +2769,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Strategy: landing surfaces board papers directly (mix of dated PDFs and/or year links). Static fetch works. Prefer the main combined board pack; filter observer notes and Q&amp;A. Pattern A/B.</t>
+          <t>Strategy: the /about/board/ landing lists board meetings with their agenda packs as direct /wp-content/uploads/YYYY/MM/ PDF links. Since spring 2026 Dorset's board meets in common with the BSW and Somerset ICB boards, so the current pack is the 'In-Common BSW, Dorset and Somerset ICB Boards agenda pack' hosted on nhsdorset.nhs.uk (earlier 2026 meetings are 'ICB Board Part One papers'). Static fetch works (plain curl 200, no WAF). Prefer the combined agenda pack; skip Part Two / confidential, minutes-only and Q&amp;A files. Pattern A. Refreshed 2026-10-10: newest pack September 2026.</t>
         </is>
       </c>
       <c r="N32" t="b">
@@ -2777,17 +2777,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+          <t>In-Common BSW, Dorset and Somerset ICB Boards agenda pack;ICB-Board-Part-One-Papers;/wp-content/uploads/YYYY/MM/</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>Part Two;Confidential;Minutes only;Q&amp;A</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=5, year_archives=1, meeting_subpages=0.</t>
+          <t>Refreshed 2026-10-10 by local browser-UA curl (200, 161KB): landing links the September 2026 'In-Common BSW, Dorset and Somerset ICB Boards agenda pack' plus the May 2026 in-common legacy board pack and the Mar/Jan 2026 ICB Board Part One papers under /wp-content/uploads/YYYY/MM/.</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>URL PATCHED 2026-10-03 (Pattern F + cluster board): NHS Cornwall and Isles of Scilly ICB now holds its ordinary board meetings jointly with NHS Devon ICB (QJK) as the 'South West Peninsula Board' (SW-PEN cluster), and the packs are published on the dedicated joint site swpboard.nhs.uk (site title 'NHS CIOS and Devon ICB'). The old own-domain page cios.icb.nhs.uk/about/meetings/ is still live but stops at the 28 May 2026 extraordinary meeting and says future dates are TBC; use it only for the pre-cluster archive (direct PDFs on docs.cios.icb.nhs.uk/DocumentsLibrary/NHSCornwallAndIslesOfScilly/Organisation/PublicMeetings/BoardMeetings/{YYYY}/{YYYYMM}/, grouped by financial year). Strategy on the new landing: static WordPress page (plain browser-UA curl works, no Playwright) listing each joint meeting with direct PDFs under /wp-content/uploads/YYYY/MM/. Naming varies by meeting: 'SWPB-Public-29.01.2026-Meeting-Papers-1.pdf', 'SWPB-Meeting-30-July-2026-Agenda-and-Papers-v4.pdf', 'SWP-Board-24.09.2026-Agenda-and-Reports.pdf'. Take the 'Meeting Papers' / 'Agenda and Papers' / 'Agenda and Reports' file as the main pack; separate 'Appendices' PDFs and individual SWPB26-NNN item PDFs accompany it, and minutes are uploaded months later. Bi-monthly cadence (Jan, Mar, May, Jul, Sep, Nov); next 26 Nov 2026. The joint AGM pack (NHS-CIOS-and-NHSD-AGM-*) is also listed. Note the swpboard.nhs.uk/meetings/ path recorded as cluster_meeting_url now 404s - this page is the live joint archive.</t>
+          <t>URL PATCHED 2026-10-03 (Pattern F + cluster board): NHS Cornwall and Isles of Scilly ICB now holds its ordinary board meetings jointly with NHS Devon ICB (QJK) as the 'South West Peninsula Board' (SW-PEN cluster), and the packs are published on the dedicated joint site swpboard.nhs.uk (site title 'NHS CIOS and Devon ICB'). The old own-domain page cios.icb.nhs.uk/about/meetings/ is still live but stops at the 28 May 2026 extraordinary meeting and says future dates are TBC; use it only for the pre-cluster archive (direct PDFs on docs.cios.icb.nhs.uk/DocumentsLibrary/NHSCornwallAndIslesOfScilly/Organisation/PublicMeetings/BoardMeetings/{YYYY}/{YYYYMM}/, grouped by financial year). Strategy on the new landing: static WordPress page (plain browser-UA curl works, no Playwright) listing each joint meeting with direct PDFs under /wp-content/uploads/YYYY/MM/. Naming varies by meeting: 'SWPB-Public-29.01.2026-Meeting-Papers-1.pdf', 'SWPB-Meeting-30-July-2026-Agenda-and-Papers-v4.pdf', 'SWP-Board-24.09.2026-Agenda-and-Reports.pdf'. Take the 'Meeting Papers' / 'Agenda and Papers' / 'Agenda and Reports' file as the main pack; separate 'Appendices' PDFs and individual SWPB26-NNN item PDFs accompany it, and minutes are uploaded months later. Bi-monthly cadence (Jan, Mar, May, Jul, Sep, Nov); next 26 Nov 2026. The joint AGM pack (NHS-CIOS-and-NHSD-AGM-*) is also listed. Note the swpboard.nhs.uk/meetings/ path recorded as cluster_meeting_url now 404s - this page is the live joint archive. Re-verified 2026-10-10: local browser-UA curl was refused with a generic '403 - Forbidden' page (shared with three trust sites that morning) while server-side WebFetch listed every 2026 pack; try WebFetch on a local 403 before repointing.</t>
         </is>
       </c>
       <c r="N36" t="b">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-03 by local browser-UA curl (200, 125KB): swpboard.nhs.uk lists the joint board's 2026 packs (29 Jan, 26 Mar, 28 May, 30 Jul, 24 Sep 2026 - SWP-Board-24.09.2026-Agenda-and-Reports.pdf); the old cios.icb.nhs.uk page stops at the 28 May 2026 extraordinary meeting.</t>
+          <t>Re-verified 2026-10-10 via server-side WebFetch (local browser-UA curl got a generic '403 - Forbidden' page this run): swpboard.nhs.uk lists the joint board's 2026 packs for 29 Jan, 26 Mar, 28 May, 30 Jul and 24 Sep 2026 (SWP-Board-24.09.2026-Agenda-and-Reports.pdf).</t>
         </is>
       </c>
     </row>

--- a/icb_urls.xlsx
+++ b/icb_urls.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 by local browser-UA curl (200, 36KB): hub links the 'Board meeting held in public on Wednesday 30 September 2026' page.</t>
+          <t>Re-verified 2026-10-17 by local browser-UA curl (200): hub links the 'Board meeting held in public on Wednesday 30 September 2026' page.</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Strategy: landing lists per-meeting entries (39 dated meeting links this run); each links to its own sub-page of PDFs (agenda, papers, finance). Filter to the main Board (skip ICP/committee/joint). Prefer the largest 'Agenda and Papers' combined PDF. Static fetch works. Pattern C.</t>
+          <t>Strategy: per-meeting sub-pages. The landing lists meetings as /meetings-and-papers/&lt;slug&gt;/ pages and has no files itself. Slugs are inconsistent and do not always match the meeting date: the 16 September 2026 meeting lives at /9-sept-2026/, and others use '11-nov-2026' or '20-january-2027', so follow the hrefs rather than constructing URLs. Each meeting page links its papers individually under /wp-content/uploads/&lt;YYYY&gt;/&lt;MM&gt;/, mostly as .docx (numbered '00-PUBLIC-AGENDA', '02a Declarations', '03 Minutes' ...) - collect the numbered items; there is usually no combined PDF. Static fetch works.</t>
         </is>
       </c>
       <c r="N6" t="b">
@@ -831,17 +831,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Agenda and Papers;Combined Pack;Public Board Pack</t>
+          <t>PUBLIC-AGENDA;numbered item files;.docx</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>Declarations-of-Interest;Gifts-and-hospitality;attending-a-board-meeting</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=0, year_archives=2, meeting_subpages=39.</t>
+          <t>2026-10-17 local browser-UA curl (200): per-meeting pages incl. /meetings-and-papers/9-sept-2026/, which holds the 16 September 2026 public board papers (00-PUBLIC-AGENDA-16-SEPTEMBER-2026-FINAL.docx and numbered items); next 18 Nov 2026.</t>
         </is>
       </c>
     </row>
@@ -1018,35 +1018,35 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Strategy: landing lists year archives (5 'Board papers 20XX' year links). The year-link URLs are Concrete CMS navigate endpoints (.../navigate/13363/NNNN) that load via AJAX — static fetch returns no PDFs from the year pages. Playwright + interactive_dom strategy (render landing, click year tabs, re-scrape DOM) recovers 9 in-window meetings. PDF titles: 'ICB Board Pack {Month YYYY}' / 'Joint ICB Cluster Board Meeting - {Month YYYY}'.</t>
+          <t>Strategy: year archives in a Concrete CMS document library. The landing links year folders as .../integrated-care-board-papers/navigate/13363/&lt;folder-id&gt; (2022=5773, 2023=5774, 2024=6160, 2025=7809, 2026=9690 as of 2026-10-17). Each year folder is a normal GET that returns static HTML listing the packs ('ICB Board Pack &lt;Month YYYY&gt;' / 'Joint ICB Cluster Board Meeting - &lt;Month YYYY&gt;') via /download_file/&lt;id&gt;/1395 (no .pdf suffix). Earlier runs recorded the year links as AJAX-only, but on 2026-10-17 a plain browser-UA fetch of the navigate URL returned the file list, so needs_playwright was dropped to false. BSOL meets as a joint cluster board with Black Country ICB, so newer packs are titled 'Joint ICB Cluster Board'.</t>
         </is>
       </c>
       <c r="N9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ICB Board Pack; Joint ICB Cluster Board Meeting; Board Papers</t>
+          <t>ICB Board Pack;Joint ICB Cluster Board Meeting;download_file/&lt;id&gt;/1395</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Committee; Q&amp;A; Confidential; Part 2</t>
+          <t>Committee;Q&amp;A;Confidential;Part 2;Modern slavery statement</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Year archives are Concrete CMS AJAX navigate endpoints. Playwright + click-each-year-tab required. March 2026 (16MB, BAF score 414) and May 2026 (9MB) packs recovered.</t>
+          <t>2026-10-17 local browser-UA curl: the 2026 year folder (navigate/13363/9690) returned static HTML listing 12 Jan, March, 'Joint ICB Cluster Board Meeting - May 2026' and '- July 2026' packs via download_file/&lt;id&gt;/1395.</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 by local browser-UA curl with --retry (200, 56KB; validator saw a connection reset): static HTML holds 'Agenda 00 Public Board 16 September 26' and the other 16 Sep 2026 items under /download/clientfiles/files/.</t>
+          <t>Re-verified 2026-10-17 by local browser-UA curl (200; validator saw a connection reset): 'Agenda 00 Public Board 16 September 26' and the other 16 Sep 2026 items under /download/clientfiles/files/.</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 by local browser-UA curl (200, 53KB): /meetings/board-papers holds the 16 September 2026 pack (Agenda 00 Public Board 16 September 26, BAF, governance log) as hwics.org.uk/download_file/&lt;id&gt;/414 links.</t>
+          <t>Re-verified 2026-10-17 by local browser-UA curl (200): 16 September 2026 pack items (e.g. Agenda 13 BAF September 2026) as hwics.org.uk/download_file/&lt;id&gt;/414 links.</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://lincolnshire.icb.nhs.uk/about-us/our-board-and-committees/icb-board-meetings/</t>
+          <t>https://lincolnshire.icb.nhs.uk/about-us/meet-the-board/icb-board-meetings/</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Strategy: landing surfaces board papers directly (mix of dated PDFs and/or year links). Static fetch works. Prefer the main combined board pack; filter observer notes and Q&amp;A. Pattern A/B.</t>
+          <t>Strategy: the landing (URL updated 2026-10-17 to the 301 target /about-us/meet-the-board/icb-board-meetings/) lists cluster board meeting dates and 'View the Board papers' links into a document library at /documents/icb-board-meeting-papers/ - year folders (icb-board-meeting-papers-2026/), then one folder per meeting ('ICB Cluster Board Meeting Papers - 16 July 2026'), then files served with ?layout=file. Lincolnshire meets as a cluster board, so titles say 'ICBs Cluster Board'. Event pages under /event/icbs-cluster-board-meeting-&lt;date&gt;/ describe meetings but hold no papers. Static fetch works.</t>
         </is>
       </c>
       <c r="N14" t="b">
@@ -1421,17 +1421,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+          <t>ICB Cluster Board Meeting Papers;public board papers;?layout=file</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>/event/ pages;Clinical and Care Directorate Strategic Board</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=0, year_archives=1, meeting_subpages=6.</t>
+          <t>2026-10-17 local browser-UA curl: stored URL 301s to /about-us/meet-the-board/icb-board-meetings/ (URL updated); the 2026 papers folder holds cluster board folders to 16 July 2026; the 17 Sep 2026 meeting is listed but no folder seen yet.</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>Predecessor hertsandwestessex.ics.nhs.uk URL 301-redirects to the Central East homepage (path dropped); the equivalent filter on the new centraleast.icb.nhs.uk domain lists dated Integrated Board packs for 1 April 2026 and 26 June 2026.</t>
+          <t>2026-10-17 local browser-UA curl (200): documents filter lists 'Papers for the Board of the ICB meeting in Public 25 September 2026' plus 26 Jun and 1 Apr 2026.</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 by local browser-UA curl (200, 218KB): the stored landing links per-meeting pages through ICB Board meeting 23 (29 Jul 2026), and the live /board-meetings/ index likewise stops at meeting 23; meeting-24 is still 404, so no board pack has appeared since July.</t>
+          <t>Re-verified 2026-10-17 by local browser-UA curl (200): per-meeting pages still stop at ICB Board meeting 23 (29 Jul 2026); meeting-24 is still 404.</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 by local browser-UA curl (200, 76KB): landing links the 22 July 2026 Board papers folder (navigate/486/2410) and the 23 Sep 2026 AGM folder (navigate/1617/2410); next board meeting 21 Oct 2026, papers to follow.</t>
+          <t>Re-verified 2026-10-17 by local browser-UA curl (200): landing links the 22 July 2026 Board papers folder and the 23 Sep 2026 AGM; next board meeting 21 Oct 2026, papers to follow.</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Strategy: dated board-pack PDFs listed directly on the landing page (17 found this run), one per meeting. Static fetch works. Prefer 'Public Board Pack' / 'Board Papers' / 'Agenda and Papers'; filter observer notes, Q&amp;A and addendums. Pattern A.</t>
+          <t>Strategy: the landing lists each board meeting (2026: 28 Jan, 1 Apr, 24 Jun, 30 Sep) with its papers as individual numbered items ('0 Agenda .pdf', '1-2 Register of Interest .pdf', '1-5 Minutes of the last meeting.pdf' ...) via Jadu-style /download/&lt;slug&gt;?ver=&lt;n&gt;&amp;doc=docm93jijm4n&lt;id&gt;.pdf. There is usually no single combined pack, so collect the numbered items for the meeting. The ICB moved to surreysussex.icb.nhs.uk on 1 April 2026; the old sussex.ics.nhs.uk site is archived and its pages now redirect to the new homepage. Static fetch works.</t>
         </is>
       </c>
       <c r="N30" t="b">
@@ -2637,17 +2637,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+          <t>numbered item PDFs (0 Agenda, 1-x ...);docm93jijm4n</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>Register of Interest;Action log</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=17, year_archives=0, meeting_subpages=0.</t>
+          <t>2026-10-17 local browser-UA curl (200): 80 itemised paper links ('0 Agenda', '1-2 Register of Interest', '1-5 Minutes of the last meeting' ...) for the 30 Sep 2026 board; next 25 Nov 2026.</t>
         </is>
       </c>
     </row>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-10 via server-side WebFetch (local browser-UA curl got a generic '403 - Forbidden' page this run): swpboard.nhs.uk lists the joint board's 2026 packs for 29 Jan, 26 Mar, 28 May, 30 Jul and 24 Sep 2026 (SWP-Board-24.09.2026-Agenda-and-Reports.pdf).</t>
+          <t>Re-verified 2026-10-17 by local browser-UA curl (200 this run): swpboard.nhs.uk lists SWP-Board-24.09.2026-Agenda-and-Reports.pdf plus appendices.</t>
         </is>
       </c>
     </row>

--- a/icb_urls.xlsx
+++ b/icb_urls.xlsx
@@ -662,7 +662,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Static landing page lists dated ICB Board meetings each linking a single combined papers PDF, confirmed for Nov and Dec 2025.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200, 74KB): 340 PDF links on the meetings-and-events listing, with October 2026 uploads present.</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 by local browser-UA curl (200): hub links the 'Board meeting held in public on Wednesday 30 September 2026' page.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): hub links the 'Board meeting held in public on Wednesday 30 September 2026' page.</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 by local browser-UA curl (200; validator saw a connection reset): 'Agenda 00 Public Board 16 September 26' and the other 16 Sep 2026 items under /download/clientfiles/files/.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200; scanner saw a connection reset): 'Agenda 00 Public Board 16 September 26' and the other 16 Sep 2026 items; next 18 Nov 2026.</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 by local browser-UA curl (200): 16 September 2026 pack items (e.g. Agenda 13 BAF September 2026) as hwics.org.uk/download_file/&lt;id&gt;/414 links.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): 16 September 2026 pack items as hwics.org.uk/download_file/&lt;id&gt;/414 links.</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>This is the correct, fully-populated Nottingham &amp; Nottinghamshire ICB Board page (title 'Our Board - NHS Nottingham and Nottinghamshire ICB'). Static-fetchable; lists every 2025-2026 meeting with direct 'Agenda and Papers' PDF links hosted on the same domain at /wp-content/uploads/sites/2/&lt;yyyy&gt;/&lt;mm&gt;/...pdf. The validator saw only 1 dated PDF likely due to lazy-loaded accordions, but a full fetch reveals the complete index (21 May 2026, 19 Mar 2026, 15 Jan 2026, 20 Nov 2025, 10 Sep 2025, 9 Jul 2025, 14 May 2025). Recent packs are named 'DLN-ICB-Board-&lt;date&gt;.pdf' reflecting the Derbyshire/Lincolnshire/Nottinghamshire cluster 'board meeting in common'; these are the Notts ICB board papers. Crawler: fetch this page and harvest the /wp-content/uploads/.../*.pdf links; prefer the 'DLN-ICB-Board-papers-&lt;date&gt;.pdf'/'ICB-Board-&lt;date&gt;.pdf' pack and the 'Cluster-Board-Meeting-Summary' for the readout. Exclude ICP and committee links.</t>
+          <t>This is the correct, fully-populated Nottingham &amp; Nottinghamshire ICB Board page (title 'Our Board - NHS Nottingham and Nottinghamshire ICB'). Static-fetchable; lists every 2025-2026 meeting with direct 'Agenda and Papers' PDF links hosted on the same domain at /wp-content/uploads/sites/2/&lt;yyyy&gt;/&lt;mm&gt;/...pdf. The validator saw only 1 dated PDF likely due to lazy-loaded accordions, but a full fetch reveals the complete index (21 May 2026, 19 Mar 2026, 15 Jan 2026, 20 Nov 2025, 10 Sep 2025, 9 Jul 2025, 14 May 2025). Recent packs are named 'DLN-ICB-Board-&lt;date&gt;.pdf' reflecting the Derbyshire/Lincolnshire/Nottinghamshire cluster 'board meeting in common'; these are the Notts ICB board papers. Crawler: fetch this page and harvest the /wp-content/uploads/.../*.pdf links; prefer the 'DLN-ICB-Board-papers-&lt;date&gt;.pdf'/'ICB-Board-&lt;date&gt;.pdf' pack and the 'Cluster-Board-Meeting-Summary' for the readout. Exclude ICP and committee links. ACCESS CHANGE 2026-10-24: the public HTML of /about-us/our-icb-board/ now arrives with an EMPTY entry-content block (41KB shell, zero PDF links) to both local browser-UA curl and server-side WebFetch, and the page now just says the Board meets in common with Derby and Derbyshire and Lincolnshire ICBs. The content still exists: GET https://notts.icb.nhs.uk/wp-json/wp/v2/pages/23824 returns the full rendered page (content.rendered, modified 2026-10-02) with every pack link, and /wp-json/wp/v2/media?search=board&amp;orderby=date lists recent uploads. All 2026 packs sit under /wp-content/uploads/sites/2/2025/08/ regardless of meeting date (DLN-ICB-Board-papers-19.03.26-1.pdf, DLN-ICB-Board-21.05.26.pdf, DLN-ICB-Open-Board-meeting-papers-16.07.2026.pdf, DLN-Board-public-Session-17.09.2026.pdf), each with a Cluster-Board-Meeting-Summary readout. Use the REST route; do not treat the empty page as a withdrawal.</t>
         </is>
       </c>
       <c r="N15" t="b">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>Page is a full board-papers index with direct dated PDF links for all 2025-2026 meetings on the same domain.</t>
+          <t>2026-10-24: served HTML now has an empty content block (no PDF links to curl or WebFetch), but the WordPress REST API (/wp-json/wp/v2/pages/23824) returns the full page: DLN-Board-public-Session-17.09.2026.pdf and Cluster-Board-Meeting-Summary-September-2026_V2.pdf newest.</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://staffsstoke.icb.nhs.uk/your-nhs-integrated-care-board/our-publications/board-papers/</t>
+          <t>https://www.staffsstoke.icb.nhs.uk/your-nhs-integrated-care-board/our-publications/board-papers/</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Pattern B + C: the board-papers landing is a static document library exposing year folders (/board-papers/2025/, /board-papers/2026/). Each year folder lists month sub-folders (e.g. /2025/november-2025/), and each month folder contains a single combined ICB Board pack file accessed via a '...?layout=file' download URL (e.g. .../november-2025/icb-board-meeting-papers-20-november-2025/?layout=file -&gt; 'COMBINED PAPERS ICB Board Meeting ... PUBLIC Session.pdf', ~6 MB). Crawl: year folder -&gt; month folder -&gt; pick the item titled 'ICB Board Meeting Papers &lt;date&gt;' and append ?layout=file. Month folders also contain unrelated items (Easy Read letters, event flyers), so prefer the combined ICB Board papers item only; this is the ICB Board collection, separate from Board briefings and committee collections.</t>
+          <t>Pattern B + C: the board-papers landing is a static document library exposing year folders (/board-papers/2025/, /board-papers/2026/). Each year folder lists month sub-folders (e.g. /2025/november-2025/), and each month folder contains a single combined ICB Board pack file accessed via a '...?layout=file' download URL (e.g. .../november-2025/icb-board-meeting-papers-20-november-2025/?layout=file -&gt; 'COMBINED PAPERS ICB Board Meeting ... PUBLIC Session.pdf', ~6 MB). Crawl: year folder -&gt; month folder -&gt; pick the item titled 'ICB Board Meeting Papers &lt;date&gt;' and append ?layout=file. Month folders also contain unrelated items (Easy Read letters, event flyers), so prefer the combined ICB Board papers item only; this is the ICB Board collection, separate from Board briefings and committee collections. Update 2026-10-24: the bare-domain URL now 301-redirects to www.staffsstoke.icb.nhs.uk (URL updated to the redirect target). The 2026 document-library folder holds January, March, April and June 2026 only; the 24 September 2026 STW-SSOT Board-in-Common pack is hosted on the partner ICB domain (www.shropshiretelfordandwrekin.nhs.uk/wp-content/uploads/NHS-STW-SSOT-Agenda-Paper-Pack-September-2026-1.pdf) and linked from www.staffsstoke.icb.nhs.uk/your-nhs-integrated-care-board/board-meetings/, which also carries YouTube recordings. Check that board-meetings page for the newest pack before concluding the library is stale.</t>
         </is>
       </c>
       <c r="N19" t="b">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>Year-&gt;month folder structure confirmed; November 2025 month folder yields one combined ICB Board papers PDF (~6.44 MB) via the ?layout=file URL.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl and WebFetch: bare-domain URL 301s to www. (DB updated); 2026 library folders stop at June 2026 and the 24 Sep 2026 STW-SSOT pack is on the partner domain shropshiretelfordandwrekin.nhs.uk.</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 by local browser-UA curl (200): per-meeting pages still stop at ICB Board meeting 23 (29 Jul 2026); meeting-24 is still 404.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): /board-meetings/ index still stops at ICB Board meeting 23 (29 Jul 2026) although 9 September 2026 is listed; meeting-24 page still 404.</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 by local browser-UA curl (200): landing links the 22 July 2026 Board papers folder and the 23 Sep 2026 AGM; next board meeting 21 Oct 2026, papers to follow.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): landing now links 'Board meeting - 21 October 2026 - agenda papers' and its recording.</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Re-confirmed 2026-09-26 via local browser-UA curl following the site's own 301 to the no-trailing-slash canonical (HTTP 200, 82KB, title 'Integrated Care Board meetings :: NHS Hampshire and Isle of Wight'): 15+ /navigate/23515/&lt;id&gt; per-meeting pages spanning 5 February 2025 to 4 November 2026, most recent held meeting 2 September 2026. DB url updated to the redirect target. Server-side WebFetch socket-hangs on this host.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): document-library navigate folders for 2026 meetings to 2 September 2026; next 4 Nov 2026.</t>
         </is>
       </c>
     </row>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>2026-09-05: WebFetch reached the page; newest 'Thames Valley ICB Board papers 15 July 2026' (10.5MB) served via the /file endpoint.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): /792-thames-valley-icb-board-papers-16-september-2026/file newest (also 15 Jul and 20 May 2026).</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Pattern C: the /events/ listing is static HTML and includes dated 'Integrated Care Board (ICB) Board meeting &lt;date&gt;' events, each linking to a per-event sub-page (/events/integrated-care-board-icb-board-meeting-&lt;date&gt;/). The event page does NOT provide a single combined pack; it lists the agenda PDFs (e.g. '00 - Agenda ICB Board Open ...') plus ~14 individual supporting paper/committee report PDFs, all hosted under bnssghealthiertogether.org.uk/wp-content/uploads/YYYY/MM/. Crawl: filter /events/ to titles containing 'ICB Board meeting' (skip ICP and standalone committee events), open the event page, then collect the '00 - Agenda ICB Board Open' PDF and all wp-content/uploads paper PDFs. Note some 2026 entries are 'Joint Cluster' ICB Board meetings.</t>
+          <t>Pattern C: the /events/ listing is static HTML and includes dated 'Integrated Care Board (ICB) Board meeting &lt;date&gt;' events, each linking to a per-event sub-page (/events/integrated-care-board-icb-board-meeting-&lt;date&gt;/). The event page does NOT provide a single combined pack; it lists the agenda PDFs (e.g. '00 - Agenda ICB Board Open ...') plus ~14 individual supporting paper/committee report PDFs, all hosted under bnssghealthiertogether.org.uk/wp-content/uploads/YYYY/MM/. Crawl: filter /events/ to titles containing 'ICB Board meeting' (skip ICP and standalone committee events), open the event page, then collect the '00 - Agenda ICB Board Open' PDF and all wp-content/uploads paper PDFs. Note some 2026 entries are 'Joint Cluster' ICB Board meetings. Note 2026-10-24: since May 2026 the ICB Board event slugs are 'joint-cluster-integrated-care-board-icb-board-meeting-&lt;d-month-yyyy&gt;' (BNSSG-GLO cluster board), alongside older 'integrated-care-board-icb-board-meeting-&lt;date&gt;' pages - match both, and skip icp-board-meeting-* and annual-general-meeting pages.</t>
         </is>
       </c>
       <c r="N34" t="b">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Per-event page for 4 December 2025 confirmed listing open/motion agenda PDFs plus ~14 individual supporting paper PDFs under wp-content/uploads; no single combined pack.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): /events/ lists joint-cluster-integrated-care-board-icb-board-meeting-30-september-2026; next 26 Nov 2026.</t>
         </is>
       </c>
     </row>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-17 by local browser-UA curl (200 this run): swpboard.nhs.uk lists SWP-Board-24.09.2026-Agenda-and-Reports.pdf plus appendices.</t>
+          <t>Re-verified 2026-10-24 by local browser-UA curl (200): swpboard.nhs.uk lists SWP-Board-24.09.2026-Agenda-and-Reports.pdf plus appendices; next 26 Nov 2026.</t>
         </is>
       </c>
     </row>

--- a/icb_urls.xlsx
+++ b/icb_urls.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-24 by local browser-UA curl (200): hub links the 'Board meeting held in public on Wednesday 30 September 2026' page.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): hub links the 'Board meeting held in public on Wednesday 30 September 2026' page.</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Confirmed dated Board entries e.g. 'Download papers for 08 December 2025' (blackcountryics.org.uk/download_file/view/4017/475) and '11 May 2026' (/download_file/view/4236/475).</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): 'Download papers for' 12 Jan, 9 Mar, 11 May, 13 Jul 2026 listed; next 9 Nov 2026.</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-24 by local browser-UA curl (200): 16 September 2026 pack items as hwics.org.uk/download_file/&lt;id&gt;/414 links.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): 16 September 2026 pack items (e.g. Agenda 13 BAF September 2026) as download_file links.</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-24 by local browser-UA curl (200): /board-meetings/ index still stops at ICB Board meeting 23 (29 Jul 2026) although 9 September 2026 is listed; meeting-24 page still 404.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): meeting index still stops at ICB Board meeting 23 (29 Jul 2026); /north-east-london-icb-board-meeting-24/ returns 404 and no later date is listed on the landing.</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-24 by local browser-UA curl (200): landing now links 'Board meeting - 21 October 2026 - agenda papers' and its recording.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): landing links the 21 October 2026 board meeting agenda papers; earlier 2026 dates 17 Jun, 22 Jul, 23 Sep.</t>
         </is>
       </c>
     </row>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Re-verified 2026-10-24 by local browser-UA curl (200): swpboard.nhs.uk lists SWP-Board-24.09.2026-Agenda-and-Reports.pdf plus appendices; next 26 Nov 2026.</t>
+          <t>Re-verified 2026-10-31 by local browser-UA curl (200): swpboard.nhs.uk lists 50 PDFs incl. 40 from 2026 (scanner saw an HTTP/2 error, transient); next 26 Nov 2026.</t>
         </is>
       </c>
     </row>
